--- a/public/assets/templates/grad-design-portfolio-checklist.xlsx
+++ b/public/assets/templates/grad-design-portfolio-checklist.xlsx
@@ -425,13 +425,13 @@
     <t>第一件放最能代表研究方向的，第二三件展現方法多樣性或思考深度，中段依主題或時間成組，最後一件留一件收尾強的。不要用最弱的作品結束。</t>
   </si>
   <si>
-    <t>搭配文章：設計研究所備審，作品集怎麼選件、排序與說明　https://tbd-web.vercel.app/pages/resources/design-graduate-portfolio.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-design-portfolio-checklist</t>
+    <t>搭配文章：設計研究所備審，作品集怎麼選件、排序與說明　https://tbd-edu.com/pages/resources/design-graduate-portfolio.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-design-portfolio-checklist</t>
   </si>
   <si>
     <t>上一階段是研究計畫書、下一階段是口試與作品集講評。作品集要和研究計畫互相支撐。</t>
   </si>
   <si>
-    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-web.vercel.app/pages/resources/tools.html</t>
+    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-edu.com/pages/resources/tools.html</t>
   </si>
   <si>
     <t>要動手的地方。判準見「先讀這裡」分頁。</t>
